--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CESUR DISTRITO OLIMPICO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CESUR DISTRITO OLIMPICO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. GONZALEZ NOGALES</t>
+          <t>P. PEREZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>36.6745</v>
+        <v>37.0838</v>
       </c>
       <c r="E2" t="n">
-        <v>27.6348</v>
+        <v>15.1335</v>
       </c>
       <c r="F2" t="n">
-        <v>9.0395</v>
+        <v>21.9501</v>
       </c>
       <c r="G2" t="n">
-        <v>4.297999999999999</v>
+        <v>31.5287</v>
       </c>
       <c r="H2" t="n">
-        <v>14.0006</v>
+        <v>29.23</v>
       </c>
       <c r="I2" t="n">
-        <v>-9.7027</v>
+        <v>2.298899999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>23.0711</v>
+        <v>49.5017</v>
       </c>
       <c r="K2" t="n">
-        <v>23.0471</v>
+        <v>41.5906</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02369999999999939</v>
+        <v>7.911700000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-18.773</v>
+        <v>-17.9731</v>
       </c>
       <c r="N2" t="n">
-        <v>-9.046700000000001</v>
+        <v>-12.3607</v>
       </c>
       <c r="O2" t="n">
-        <v>-9.7264</v>
+        <v>-5.6124</v>
       </c>
       <c r="P2" t="n">
-        <v>2.8962</v>
+        <v>-10.2332</v>
       </c>
       <c r="Q2" t="n">
-        <v>-27.0314</v>
+        <v>-48.0766</v>
       </c>
       <c r="R2" t="n">
-        <v>29.927</v>
+        <v>37.8433</v>
       </c>
       <c r="S2" t="n">
-        <v>15.8469</v>
+        <v>6.1866</v>
       </c>
       <c r="T2" t="n">
-        <v>14.3347</v>
+        <v>-2.5119</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5124</v>
+        <v>8.698599999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>13.6332</v>
+        <v>9.6015</v>
       </c>
       <c r="W2" t="n">
-        <v>17.26</v>
+        <v>16.2199</v>
       </c>
       <c r="X2" t="n">
-        <v>-3.6268</v>
+        <v>-6.6184</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. PEREZ FERNANDEZ</t>
+          <t>J. GONZALEZ NOGALES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>29.2127</v>
+        <v>33.9144</v>
       </c>
       <c r="E3" t="n">
-        <v>3.956499999999999</v>
+        <v>22.6571</v>
       </c>
       <c r="F3" t="n">
-        <v>25.2561</v>
+        <v>11.2575</v>
       </c>
       <c r="G3" t="n">
-        <v>31.5287</v>
+        <v>4.297999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>29.23</v>
+        <v>14.0006</v>
       </c>
       <c r="I3" t="n">
-        <v>2.298899999999999</v>
+        <v>-9.7027</v>
       </c>
       <c r="J3" t="n">
-        <v>49.5017</v>
+        <v>23.0711</v>
       </c>
       <c r="K3" t="n">
-        <v>41.5906</v>
+        <v>23.0471</v>
       </c>
       <c r="L3" t="n">
-        <v>7.911700000000001</v>
+        <v>0.02369999999999939</v>
       </c>
       <c r="M3" t="n">
-        <v>-17.9731</v>
+        <v>-18.773</v>
       </c>
       <c r="N3" t="n">
-        <v>-12.3607</v>
+        <v>-9.046700000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-5.6124</v>
+        <v>-9.7264</v>
       </c>
       <c r="P3" t="n">
-        <v>-10.2332</v>
+        <v>2.8962</v>
       </c>
       <c r="Q3" t="n">
-        <v>-48.0766</v>
+        <v>-27.0314</v>
       </c>
       <c r="R3" t="n">
-        <v>37.8433</v>
+        <v>29.927</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6845</v>
+        <v>13.0871</v>
       </c>
       <c r="T3" t="n">
-        <v>-13.689</v>
+        <v>9.3567</v>
       </c>
       <c r="U3" t="n">
-        <v>12.0045</v>
+        <v>3.7304</v>
       </c>
       <c r="V3" t="n">
-        <v>9.6015</v>
+        <v>13.6332</v>
       </c>
       <c r="W3" t="n">
-        <v>16.2199</v>
+        <v>17.26</v>
       </c>
       <c r="X3" t="n">
-        <v>-6.6184</v>
+        <v>-3.6268</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>26.5919</v>
+        <v>32.529</v>
       </c>
       <c r="E4" t="n">
-        <v>18.7847</v>
+        <v>22.2391</v>
       </c>
       <c r="F4" t="n">
-        <v>7.807</v>
+        <v>10.2896</v>
       </c>
       <c r="G4" t="n">
         <v>31.8308</v>
@@ -766,13 +766,13 @@
         <v>36.6847</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7172999999999998</v>
+        <v>6.654199999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.4908</v>
+        <v>0.9637000000000002</v>
       </c>
       <c r="U4" t="n">
-        <v>3.2079</v>
+        <v>5.6907</v>
       </c>
       <c r="V4" t="n">
         <v>10.2624</v>
@@ -799,13 +799,13 @@
         <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>23.7759</v>
+        <v>19.0421</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6398</v>
+        <v>-0.7447999999999997</v>
       </c>
       <c r="F5" t="n">
-        <v>19.1361</v>
+        <v>19.787</v>
       </c>
       <c r="G5" t="n">
         <v>15.7549</v>
@@ -844,13 +844,13 @@
         <v>30.12</v>
       </c>
       <c r="S5" t="n">
-        <v>13.0291</v>
+        <v>8.2958</v>
       </c>
       <c r="T5" t="n">
-        <v>7.3847</v>
+        <v>2.0001</v>
       </c>
       <c r="U5" t="n">
-        <v>5.6444</v>
+        <v>6.2957</v>
       </c>
       <c r="V5" t="n">
         <v>0.9770999999999994</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. LUENGO NEVADO</t>
+          <t>S. HERTEL HERMOSA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>14.2255</v>
+        <v>9.7614</v>
       </c>
       <c r="E6" t="n">
-        <v>12.313</v>
+        <v>2.934600000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9124</v>
+        <v>6.827</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2102</v>
+        <v>4.365299999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>9.2102</v>
+        <v>3.5699</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.0002</v>
+        <v>0.7955000000000009</v>
       </c>
       <c r="J6" t="n">
-        <v>11.593</v>
+        <v>14.5738</v>
       </c>
       <c r="K6" t="n">
-        <v>10.7338</v>
+        <v>9.5093</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8592</v>
+        <v>5.064699999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-5.3829</v>
+        <v>-10.2083</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5235</v>
+        <v>-5.9391</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.8594</v>
+        <v>-4.2689</v>
       </c>
       <c r="P6" t="n">
-        <v>5.02</v>
+        <v>0.7722</v>
       </c>
       <c r="Q6" t="n">
-        <v>-10.2333</v>
+        <v>-21.0456</v>
       </c>
       <c r="R6" t="n">
-        <v>15.2529</v>
+        <v>21.8177</v>
       </c>
       <c r="S6" t="n">
-        <v>13.4928</v>
+        <v>2.0479</v>
       </c>
       <c r="T6" t="n">
-        <v>11.5799</v>
+        <v>0.9403</v>
       </c>
       <c r="U6" t="n">
-        <v>1.913</v>
+        <v>1.1078</v>
       </c>
       <c r="V6" t="n">
-        <v>-10.4976</v>
+        <v>2.5756</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6266999999999998</v>
+        <v>8.4659</v>
       </c>
       <c r="X6" t="n">
-        <v>-9.871</v>
+        <v>-5.8903</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. CORREA BOULATOVA</t>
+          <t>C. LUENGO NEVADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>10.5268</v>
+        <v>6.8971</v>
       </c>
       <c r="E7" t="n">
-        <v>17.8238</v>
+        <v>6.163</v>
       </c>
       <c r="F7" t="n">
-        <v>-7.2969</v>
+        <v>0.7341000000000002</v>
       </c>
       <c r="G7" t="n">
-        <v>1.603</v>
+        <v>6.2102</v>
       </c>
       <c r="H7" t="n">
-        <v>10.8504</v>
+        <v>9.2102</v>
       </c>
       <c r="I7" t="n">
-        <v>-9.247400000000001</v>
+        <v>-3.0002</v>
       </c>
       <c r="J7" t="n">
-        <v>27.9986</v>
+        <v>11.593</v>
       </c>
       <c r="K7" t="n">
-        <v>26.2419</v>
+        <v>10.7338</v>
       </c>
       <c r="L7" t="n">
-        <v>1.757</v>
+        <v>0.8592</v>
       </c>
       <c r="M7" t="n">
-        <v>-26.3954</v>
+        <v>-5.3829</v>
       </c>
       <c r="N7" t="n">
-        <v>-15.3919</v>
+        <v>-1.5235</v>
       </c>
       <c r="O7" t="n">
-        <v>-11.0042</v>
+        <v>-3.8594</v>
       </c>
       <c r="P7" t="n">
-        <v>9.0748</v>
+        <v>5.02</v>
       </c>
       <c r="Q7" t="n">
-        <v>-23.1695</v>
+        <v>-10.2333</v>
       </c>
       <c r="R7" t="n">
-        <v>32.244</v>
+        <v>15.2529</v>
       </c>
       <c r="S7" t="n">
-        <v>27.8985</v>
+        <v>6.164800000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>28.2337</v>
+        <v>5.4298</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3356</v>
+        <v>0.7348000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-28.0493</v>
+        <v>-10.4976</v>
       </c>
       <c r="W7" t="n">
-        <v>-15.2397</v>
+        <v>-0.6266999999999998</v>
       </c>
       <c r="X7" t="n">
-        <v>-12.8098</v>
+        <v>-9.871</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. LAPUSTE</t>
+          <t>M. ALONSO MENOR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9518</v>
+        <v>3.496699999999998</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9518</v>
+        <v>-3.0111</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>6.507899999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9518</v>
+        <v>-5.167099999999998</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9518</v>
+        <v>0.9322999999999997</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-6.0994</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9518</v>
+        <v>10.1253</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9518</v>
+        <v>8.1869</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.938900000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-15.2923</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-7.254300000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-8.0379</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-31.8583</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>30.6995</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>5.427199999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.1247</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>5.5517</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>4.3951</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>18.8458</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-14.451</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. HERTEL HERMOSA</t>
+          <t>S. LAPUSTE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6081000000000005</v>
+        <v>0.9518</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.857200000000001</v>
+        <v>0.9518</v>
       </c>
       <c r="F9" t="n">
-        <v>4.465</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>4.365299999999999</v>
+        <v>0.9518</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5699</v>
+        <v>0.9518</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7955000000000009</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>14.5738</v>
+        <v>0.9518</v>
       </c>
       <c r="K9" t="n">
-        <v>9.5093</v>
+        <v>0.9518</v>
       </c>
       <c r="L9" t="n">
-        <v>5.064699999999999</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-10.2083</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-5.9391</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.2689</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7722</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-21.0456</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>21.8177</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-7.1051</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-5.8513</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.2539</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>2.5756</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>8.4659</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-5.8903</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.698</v>
+        <v>-0.5355</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1107</v>
+        <v>1.0269</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5873</v>
+        <v>-1.5625</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2288999999999999</v>
@@ -1234,13 +1234,13 @@
         <v>1.5446</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3421</v>
+        <v>0.8204</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6898</v>
+        <v>0.4478</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3477</v>
+        <v>0.3727</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5133</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MUÑOZ FERRERO</t>
+          <t>I. CORREA BOULATOVA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2496</v>
+        <v>-2.0926</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2006</v>
+        <v>2.8622</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0492</v>
+        <v>-4.954699999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0427</v>
+        <v>1.603</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1864</v>
+        <v>10.8504</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.229</v>
+        <v>-9.247400000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.628</v>
+        <v>27.9986</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6696</v>
+        <v>26.2419</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2976</v>
+        <v>1.757</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4146</v>
+        <v>-26.3954</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4832</v>
+        <v>-15.3919</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9314</v>
+        <v>-11.0042</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7723</v>
+        <v>9.0748</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9308</v>
+        <v>-23.1695</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1585</v>
+        <v>32.244</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1491</v>
+        <v>15.2791</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3583</v>
+        <v>13.2722</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5073000000000001</v>
+        <v>2.0066</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2856</v>
+        <v>-28.0493</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-15.2397</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2856</v>
+        <v>-12.8098</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. MONTBLANC GONZALEZ</t>
+          <t>A. MUÑOZ FERRERO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4528</v>
+        <v>-3.0799</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4828</v>
+        <v>-2.304</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02990000000000004</v>
+        <v>-0.776</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8499</v>
+        <v>-2.0427</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8957999999999999</v>
+        <v>0.1864</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9540999999999999</v>
+        <v>-2.229</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2691000000000001</v>
+        <v>-0.628</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.0331</v>
+        <v>0.6696</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3022</v>
+        <v>-1.2976</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.119</v>
+        <v>-1.4146</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1372</v>
+        <v>-0.4832</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.2563</v>
+        <v>-0.9314</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.5792999999999999</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.0547</v>
+        <v>-1.9308</v>
       </c>
       <c r="R12" t="n">
-        <v>3.4754</v>
+        <v>1.1585</v>
       </c>
       <c r="S12" t="n">
-        <v>0.204</v>
+        <v>0.0206</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3027</v>
+        <v>0.2548</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.09870000000000001</v>
+        <v>-0.2342</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. GARCIA NAVARRO</t>
+          <t>M. MONTBLANC GONZALEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.603600000000001</v>
+        <v>-3.1467</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.6286</v>
+        <v>-3.2759</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02499999999999991</v>
+        <v>0.1293</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.9529000000000001</v>
+        <v>-1.8499</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6410000000000005</v>
+        <v>-0.8957999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3119999999999999</v>
+        <v>-0.9540999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>5.0527</v>
+        <v>0.2691000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8451</v>
+        <v>-1.0331</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2076</v>
+        <v>1.3022</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.0057</v>
+        <v>-2.119</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.4862</v>
+        <v>0.1372</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.5193</v>
+        <v>-2.2563</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.4062</v>
+        <v>-0.5792999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-11.1986</v>
+        <v>-4.0547</v>
       </c>
       <c r="R13" t="n">
-        <v>5.7923</v>
+        <v>3.4754</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6702</v>
+        <v>0.5101</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0465</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6237</v>
+        <v>0.0005000000000000004</v>
       </c>
       <c r="V13" t="n">
-        <v>0.08529999999999999</v>
+        <v>-1.2277</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4707</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.3854</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. BAQUEICOA PADRON</t>
+          <t>M. ESTEBANEZ ESCUDERO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.916</v>
+        <v>-3.6237</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.9099</v>
+        <v>-8.1754</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.006</v>
+        <v>4.551399999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.0554</v>
+        <v>-12.2303</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.1172</v>
+        <v>5.410699999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9382</v>
+        <v>-17.6412</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5653</v>
+        <v>-3.173</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.5653</v>
+        <v>8.6638</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-11.8368</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4901</v>
+        <v>-9.057600000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5519000000000001</v>
+        <v>-3.253</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9382</v>
+        <v>-5.8046</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.1585</v>
+        <v>18.5353</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1239</v>
+        <v>-11.778</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9654</v>
+        <v>30.3129</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4743</v>
+        <v>6.4413</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2207</v>
+        <v>0.7646999999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2536</v>
+        <v>5.6766</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2277</v>
+        <v>-16.37</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>6.0106</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2277</v>
+        <v>-22.3806</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. LOZANO ESCOBAR</t>
+          <t>D. GARCIA NAVARRO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.2658</v>
+        <v>-4.384399999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.6486</v>
+        <v>-4.138800000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.6173</v>
+        <v>-0.2454000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.3802</v>
+        <v>-0.9529000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7932</v>
+        <v>-0.6410000000000005</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.587</v>
+        <v>-0.3119999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.2348</v>
+        <v>5.0527</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.586</v>
+        <v>3.8451</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6488</v>
+        <v>1.2076</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1454</v>
+        <v>-6.0057</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2072</v>
+        <v>-4.4862</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9381999999999999</v>
+        <v>-1.5193</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-5.4062</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1931</v>
+        <v>-11.1986</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1931</v>
+        <v>5.7923</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0867</v>
+        <v>1.8895</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2207</v>
+        <v>0.5363</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8658999999999999</v>
+        <v>1.3532</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.7989</v>
+        <v>0.08529999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.4707</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.7989</v>
+        <v>-1.3854</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ESTEBANEZ ESCUDERO</t>
+          <t>D. LOZANO ESCOBAR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>-5.837900000000001</v>
+        <v>-4.8066</v>
       </c>
       <c r="E16" t="n">
-        <v>-11.7334</v>
+        <v>-1.3383</v>
       </c>
       <c r="F16" t="n">
-        <v>5.8958</v>
+        <v>-3.4683</v>
       </c>
       <c r="G16" t="n">
-        <v>-12.2303</v>
+        <v>-2.3802</v>
       </c>
       <c r="H16" t="n">
-        <v>5.410699999999999</v>
+        <v>-0.7932</v>
       </c>
       <c r="I16" t="n">
-        <v>-17.6412</v>
+        <v>-1.587</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.173</v>
+        <v>-1.2348</v>
       </c>
       <c r="K16" t="n">
-        <v>8.6638</v>
+        <v>-0.586</v>
       </c>
       <c r="L16" t="n">
-        <v>-11.8368</v>
+        <v>-0.6488</v>
       </c>
       <c r="M16" t="n">
-        <v>-9.057600000000001</v>
+        <v>-1.1454</v>
       </c>
       <c r="N16" t="n">
-        <v>-3.253</v>
+        <v>-0.2072</v>
       </c>
       <c r="O16" t="n">
-        <v>-5.8046</v>
+        <v>-0.9381999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>18.5353</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-11.778</v>
+        <v>-0.1931</v>
       </c>
       <c r="R16" t="n">
-        <v>30.3129</v>
+        <v>0.1931</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2275</v>
+        <v>-0.6274000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.7934</v>
+        <v>0.0895</v>
       </c>
       <c r="U16" t="n">
-        <v>7.0207</v>
+        <v>-0.7169000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-16.37</v>
+        <v>-1.7989</v>
       </c>
       <c r="W16" t="n">
-        <v>6.0106</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-22.3806</v>
+        <v>-1.7989</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. BADAMI</t>
+          <t>L. BAQUEICOA PADRON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>-7.5187</v>
+        <v>-4.8621</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4345</v>
+        <v>-2.8065</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.084300000000001</v>
+        <v>-2.0556</v>
       </c>
       <c r="G17" t="n">
-        <v>-5.579</v>
+        <v>-2.0554</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.958</v>
+        <v>-1.1172</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.6209</v>
+        <v>-0.9382</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.3706</v>
+        <v>-0.5653</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.0262</v>
+        <v>-0.5653</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6557000000000001</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.2085</v>
+        <v>-1.4901</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9318</v>
+        <v>-0.5519000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.2766</v>
+        <v>-0.9382</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3862</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.1239</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7377</v>
+        <v>0.9654</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3305</v>
+        <v>-0.4206</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4886</v>
+        <v>-0.1173</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1582</v>
+        <v>-0.3033</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.8842</v>
+        <v>-1.2277</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.4554</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. ALONSO MENOR</t>
+          <t>F. BADAMI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>-9.712400000000001</v>
+        <v>-7.891</v>
       </c>
       <c r="E18" t="n">
-        <v>-14.7806</v>
+        <v>-2.0551</v>
       </c>
       <c r="F18" t="n">
-        <v>5.068199999999999</v>
+        <v>-5.835999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.167099999999998</v>
+        <v>-5.579</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9322999999999997</v>
+        <v>-3.958</v>
       </c>
       <c r="I18" t="n">
-        <v>-6.0994</v>
+        <v>-1.6209</v>
       </c>
       <c r="J18" t="n">
-        <v>10.1253</v>
+        <v>-1.3706</v>
       </c>
       <c r="K18" t="n">
-        <v>8.1869</v>
+        <v>-2.0262</v>
       </c>
       <c r="L18" t="n">
-        <v>1.938900000000001</v>
+        <v>0.6557000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-15.2923</v>
+        <v>-4.2085</v>
       </c>
       <c r="N18" t="n">
-        <v>-7.254300000000001</v>
+        <v>-1.9318</v>
       </c>
       <c r="O18" t="n">
-        <v>-8.0379</v>
+        <v>-2.2766</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1585</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q18" t="n">
-        <v>-31.8583</v>
+        <v>-2.1239</v>
       </c>
       <c r="R18" t="n">
-        <v>30.6995</v>
+        <v>1.7377</v>
       </c>
       <c r="S18" t="n">
-        <v>-7.7823</v>
+        <v>-0.04189999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-11.8944</v>
+        <v>0.8683</v>
       </c>
       <c r="U18" t="n">
-        <v>4.1118</v>
+        <v>-0.9098000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>4.3951</v>
+        <v>-1.8842</v>
       </c>
       <c r="W18" t="n">
-        <v>18.8458</v>
+        <v>0.5712</v>
       </c>
       <c r="X18" t="n">
-        <v>-14.451</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>-11.6781</v>
+        <v>-8.485600000000002</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.677700000000001</v>
+        <v>-3.450400000000002</v>
       </c>
       <c r="F19" t="n">
-        <v>-6</v>
+        <v>-5.034699999999999</v>
       </c>
       <c r="G19" t="n">
         <v>-10.739</v>
@@ -1936,13 +1936,13 @@
         <v>42.0909</v>
       </c>
       <c r="S19" t="n">
-        <v>5.019600000000001</v>
+        <v>8.212300000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1753</v>
+        <v>2.0518</v>
       </c>
       <c r="U19" t="n">
-        <v>5.1954</v>
+        <v>6.1605</v>
       </c>
       <c r="V19" t="n">
         <v>-13.6819</v>
@@ -1969,13 +1969,13 @@
         <v>22</v>
       </c>
       <c r="D20" t="n">
-        <v>-17.1146</v>
+        <v>-13.809</v>
       </c>
       <c r="E20" t="n">
-        <v>-13.0528</v>
+        <v>-10.2326</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.0617</v>
+        <v>-3.5761</v>
       </c>
       <c r="G20" t="n">
         <v>-8.497299999999999</v>
@@ -2014,13 +2014,13 @@
         <v>21.6247</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6717</v>
+        <v>1.6337</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1705999999999997</v>
+        <v>2.6494</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.501</v>
+        <v>-1.0154</v>
       </c>
       <c r="V20" t="n">
         <v>-3.2772</v>
@@ -2047,13 +2047,13 @@
         <v>18</v>
       </c>
       <c r="D21" t="n">
-        <v>-30.2147</v>
+        <v>-32.7941</v>
       </c>
       <c r="E21" t="n">
-        <v>-16.1342</v>
+        <v>-20.0847</v>
       </c>
       <c r="F21" t="n">
-        <v>-14.0803</v>
+        <v>-12.7095</v>
       </c>
       <c r="G21" t="n">
         <v>-21.2639</v>
@@ -2092,13 +2092,13 @@
         <v>26.2586</v>
       </c>
       <c r="S21" t="n">
-        <v>10.2255</v>
+        <v>7.646199999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>7.164</v>
+        <v>3.2136</v>
       </c>
       <c r="U21" t="n">
-        <v>3.0614</v>
+        <v>4.4325</v>
       </c>
       <c r="V21" t="n">
         <v>-9.7157</v>
@@ -2125,16 +2125,16 @@
         <v>26</v>
       </c>
       <c r="D22" t="n">
-        <v>38.305</v>
+        <v>54.16509999999998</v>
       </c>
       <c r="E22" t="n">
-        <v>5.452799999999993</v>
+        <v>12.3506</v>
       </c>
       <c r="F22" t="n">
-        <v>32.852</v>
+        <v>41.81510000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>23.55609999999999</v>
+        <v>23.55610000000001</v>
       </c>
       <c r="H22" t="n">
         <v>82.4375</v>
@@ -2161,7 +2161,7 @@
         <v>-93.70839999999998</v>
       </c>
       <c r="P22" t="n">
-        <v>-10.619</v>
+        <v>-10.61899999999999</v>
       </c>
       <c r="Q22" t="n">
         <v>-380.3665999999999</v>
@@ -2170,16 +2170,16 @@
         <v>369.7432</v>
       </c>
       <c r="S22" t="n">
-        <v>73.3661</v>
+        <v>89.2269</v>
       </c>
       <c r="T22" t="n">
-        <v>33.69709999999999</v>
+        <v>40.5947</v>
       </c>
       <c r="U22" t="n">
-        <v>39.6687</v>
+        <v>48.6327</v>
       </c>
       <c r="V22" t="n">
-        <v>-47.99890000000001</v>
+        <v>-47.9989</v>
       </c>
       <c r="W22" t="n">
         <v>104.7069</v>
